--- a/results/Int All Data 0.9/Linea_fi_all.xlsx
+++ b/results/Int All Data 0.9/Linea_fi_all.xlsx
@@ -1306,7 +1306,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.0231335952848723 +/- 0.001679304616628569</t>
+          <t>0.023182711198428286 +/- 0.001754476532366574</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="EJ2" t="inlineStr">
         <is>
-          <t>0.003732809430255379 +/- 0.0010113585600183507</t>
+          <t>0.0036836935166993934 +/- 0.0010591286175268824</t>
         </is>
       </c>
       <c r="EK2" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="ET2" t="inlineStr">
         <is>
-          <t>0.003487229862475427 +/- 0.0008908819816904188</t>
+          <t>0.0035363457760314242 +/- 0.0008731035773394407</t>
         </is>
       </c>
       <c r="EU2" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.0013082155939298178 +/- 0.0006721733426826251</t>
+          <t>0.0012558869701726149 +/- 0.000627943485086326</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="EX4" t="inlineStr">
         <is>
-          <t>0.00036144578313250796 +/- 0.0008171481907379749</t>
+          <t>0.00030120481927709 +/- 0.000773809191485847</t>
         </is>
       </c>
       <c r="EY4" t="inlineStr">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="CY6" t="inlineStr">
         <is>
-          <t>0.02664455500276395 +/- 0.003844187650793506</t>
+          <t>0.026589275843007177 +/- 0.0037933750059254137</t>
         </is>
       </c>
       <c r="CZ6" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="EJ9" t="inlineStr">
         <is>
-          <t>0.0012292891501871183 +/- 0.0005879208979155665</t>
+          <t>0.0011758417958311561 +/- 0.0005756456234243302</t>
         </is>
       </c>
       <c r="EK9" t="inlineStr">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.001373134328358161 +/- 0.001888870688902253</t>
+          <t>0.0014925373134327847 +/- 0.0019845695687874206</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>0.02561194029850744 +/- 0.005275734115848443</t>
+          <t>0.02555223880597013 +/- 0.005264574969563842</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>0.00011940298507461256 +/- 0.0004467650611073421</t>
+          <t>0.00023880597014924732 +/- 0.0005471732173081453</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.014459102902374621 +/- 0.000978746015355751</t>
+          <t>-0.014564643799472244 +/- 0.001006795990941373</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>-0.006649076517150365 +/- 0.0025548746040971373</t>
+          <t>-0.006701846965699176 +/- 0.00243030690019408</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>-0.0037994722955144835 +/- 0.001665407265230552</t>
+          <t>-0.003746701846965672 +/- 0.0016426788829839959</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
